--- a/app/resource/naukri_job_links.xlsx
+++ b/app/resource/naukri_job_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Knowledge\GenAI\project-job-generator\app\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A0BAB0-F31C-4068-ABA1-5C77CD60D1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEEFBD7-496A-47F3-92AA-744CDCFBE6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
   <si>
     <t>Technology</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>chaturvedi.abhishek10@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.naukri.com/application-scientist-jobs-in-bengaluru?expJD=true</t>
   </si>
 </sst>
 </file>
@@ -546,8 +549,8 @@
       <c r="E2" t="s">
         <v>40</v>
       </c>
-      <c r="G2" t="s">
-        <v>15</v>
+      <c r="G2" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
@@ -592,7 +595,7 @@
       <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H4" t="s">
@@ -742,6 +745,8 @@
     <hyperlink ref="G3" r:id="rId1" xr:uid="{5F8ED48D-3D57-4E81-9686-9B883336C34D}"/>
     <hyperlink ref="G6" r:id="rId2" xr:uid="{16DEDEF9-C7AF-49AD-886B-C37C4786A29B}"/>
     <hyperlink ref="G8" r:id="rId3" xr:uid="{A3CDC06F-0377-455E-A08A-DA3F1B19C623}"/>
+    <hyperlink ref="G2" r:id="rId4" xr:uid="{8B802716-F219-41E8-9720-EFF61AC945CD}"/>
+    <hyperlink ref="G4" r:id="rId5" xr:uid="{8713F612-F30C-4132-B7ED-126EA8227D99}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
